--- a/Luban/DataTables/Datas/Dictionary.xlsx
+++ b/Luban/DataTables/Datas/Dictionary.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>##var</t>
   </si>
@@ -72,6 +72,36 @@
   </si>
   <si>
     <t>繁中</t>
+  </si>
+  <si>
+    <t>商店</t>
+  </si>
+  <si>
+    <t>Shop</t>
+  </si>
+  <si>
+    <t>英雄</t>
+  </si>
+  <si>
+    <t>Hero</t>
+  </si>
+  <si>
+    <t>游戏</t>
+  </si>
+  <si>
+    <t>Game</t>
+  </si>
+  <si>
+    <t>事件</t>
+  </si>
+  <si>
+    <t>Event</t>
+  </si>
+  <si>
+    <t>设置</t>
+  </si>
+  <si>
+    <t>Setting</t>
   </si>
 </sst>
 </file>
@@ -1013,7 +1043,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="20.375" style="1" customWidth="1"/>
@@ -1091,7 +1121,6 @@
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
         <v>12</v>
       </c>
@@ -1102,54 +1131,59 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="2:2">
+    <row r="5" spans="2:5">
       <c r="B5" s="1">
-        <v>1</v>
+        <v>100101</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:2">
+    <row r="6" spans="2:5">
       <c r="B6" s="1">
-        <v>2</v>
+        <v>100102</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="7" spans="2:2">
+    <row r="7" spans="2:5">
       <c r="B7" s="1">
-        <v>3</v>
+        <v>100103</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:2">
+    <row r="8" spans="2:5">
       <c r="B8" s="1">
-        <v>4</v>
+        <v>100104</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="9" spans="2:2">
+    <row r="9" spans="2:5">
       <c r="B9" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2">
-      <c r="B10" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2">
-      <c r="B11" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2">
-      <c r="B12" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2">
-      <c r="B13" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2">
-      <c r="B14" s="1">
-        <v>10</v>
+        <v>100105</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/DataTables/Datas/Dictionary.xlsx
+++ b/Luban/DataTables/Datas/Dictionary.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26880" windowHeight="9285"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
   <si>
     <t>##var</t>
   </si>
@@ -99,6 +99,24 @@
   </si>
   <si>
     <t>星2</t>
+  </si>
+  <si>
+    <t>钻石礼包1</t>
+  </si>
+  <si>
+    <t>钻石礼包2</t>
+  </si>
+  <si>
+    <t>钻石礼包3</t>
+  </si>
+  <si>
+    <t>钻石礼包4</t>
+  </si>
+  <si>
+    <t>钻石礼包5</t>
+  </si>
+  <si>
+    <t>钻石礼包6</t>
   </si>
   <si>
     <t>商店</t>
@@ -1073,7 +1091,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="20.375" style="2" customWidth="1"/>
@@ -1170,7 +1188,6 @@
       <c r="B6" s="2">
         <v>1001</v>
       </c>
-      <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
@@ -1179,7 +1196,6 @@
       <c r="B7" s="2">
         <v>1002</v>
       </c>
-      <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
         <v>16</v>
       </c>
@@ -1188,7 +1204,6 @@
       <c r="B8" s="2">
         <v>1010</v>
       </c>
-      <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
         <v>17</v>
       </c>
@@ -1197,7 +1212,6 @@
       <c r="B9" s="2">
         <v>1011</v>
       </c>
-      <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
         <v>18</v>
       </c>
@@ -1206,7 +1220,6 @@
       <c r="B10" s="2">
         <v>1012</v>
       </c>
-      <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
         <v>19</v>
       </c>
@@ -1215,7 +1228,6 @@
       <c r="B11" s="2">
         <v>1013</v>
       </c>
-      <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
         <v>20</v>
       </c>
@@ -1224,7 +1236,6 @@
       <c r="B12" s="2">
         <v>1014</v>
       </c>
-      <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
         <v>21</v>
       </c>
@@ -1233,7 +1244,6 @@
       <c r="B13" s="2">
         <v>1015</v>
       </c>
-      <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
         <v>22</v>
       </c>
@@ -1246,70 +1256,122 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
+    <row r="15" s="1" customFormat="1" spans="1:1">
+      <c r="A15" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" spans="1:1">
-      <c r="A16" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5">
+    <row r="16" spans="2:4">
+      <c r="B16" s="2">
+        <v>10001</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
       <c r="B17" s="2">
-        <v>100101</v>
-      </c>
-      <c r="C17" s="2"/>
+        <v>10002</v>
+      </c>
       <c r="D17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="2:5">
+    <row r="18" spans="2:4">
       <c r="B18" s="2">
-        <v>100102</v>
+        <v>10003</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E18" s="2" t="s">
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19" s="2">
+        <v>10004</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="2:5">
-      <c r="B19" s="2">
+    <row r="20" spans="2:4">
+      <c r="B20" s="2">
+        <v>10005</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="B21" s="2">
+        <v>10006</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5">
+      <c r="B24" s="2">
+        <v>100101</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5">
+      <c r="B25" s="2">
+        <v>100102</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5">
+      <c r="B26" s="2">
         <v>100103</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5">
-      <c r="B20" s="2">
+      <c r="D26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="B27" s="2">
         <v>100104</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5">
-      <c r="B21" s="2">
+      <c r="D27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5">
+      <c r="B28" s="2">
         <v>100105</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>33</v>
+      <c r="D28" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
